--- a/data/trans_orig/P25D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>52091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35849</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33205</t>
+          <t>30360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76631</t>
+          <t>74545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,82 +971,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13279</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>14478</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>32241</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14048</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>5498</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>32485</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>35236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>290472</t>
+          <t>296046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>351543</t>
+          <t>353099</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249803</t>
+          <t>247494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>283950</t>
+          <t>283763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>557372</t>
+          <t>559812</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>624976</t>
+          <t>622951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>29571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>22807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54360</t>
+          <t>53367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,77 +1653,77 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>10089</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>22297</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28538</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>343359</t>
+          <t>345342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>383175</t>
+          <t>384049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>456689</t>
+          <t>456444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>488214</t>
+          <t>487584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>810530</t>
+          <t>809115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>863014</t>
+          <t>861366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>52145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15097</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>477740</t>
+          <t>478511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>503827</t>
+          <t>503982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,47 +2900,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>507664</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>496905</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>515021</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>93,97%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>507664</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>497063</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>515318</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>983258</t>
+          <t>984924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1014137</t>
+          <t>1016299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26679</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>43833</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>25949</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>59728</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>3,75%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>43833</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>26474</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>59171</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,47 +3243,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14009</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6880</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>37616</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>14009</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>7070</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44983</t>
+          <t>40612</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>584076</t>
+          <t>601357</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>857</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>777722</t>
+          <t>758973</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>273624</t>
+          <t>252642</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>827390</t>
+          <t>827449</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,47 +3695,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>667313</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>646515</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>677219</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
           <t>93,78%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>667313</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>645468</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>677838</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>752456</t>
+          <t>775126</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1497276</t>
+          <t>1498067</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,47 +3960,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>22755</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>32320</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,47%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>22755</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>16675</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>31040</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,47 +4299,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>8376</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,47 +4397,47 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>514301</t>
+          <t>515649</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>535267</t>
+          <t>535978</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>516352</t>
+          <t>516044</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>528974</t>
+          <t>529603</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1035572</t>
+          <t>1036231</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1060904</t>
+          <t>1061493</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -5044,82 +5044,82 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2961</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>495</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>347098</t>
+          <t>346142</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>358972</t>
+          <t>358894</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>578461</t>
+          <t>578247</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>600829</t>
+          <t>601232</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>930330</t>
+          <t>931676</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>958872</t>
+          <t>959172</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5726,97 +5726,97 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>377</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -5839,97 +5839,97 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5952,97 +5952,97 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>267379</t>
+          <t>267990</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>278088</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>406266</t>
+          <t>405541</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>415843</t>
+          <t>415782</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>677207</t>
+          <t>677329</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>691075</t>
+          <t>691885</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>83247</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>140157</t>
+          <t>141201</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>90221</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>137908</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>188496</t>
+          <t>187718</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>263382</t>
+          <t>261841</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>34956</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>71688</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,47 +6458,47 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>92141</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>118721</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>92141</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>72536</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>119429</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1047477</t>
+          <t>1088058</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>42891</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1254547</t>
+          <t>1207587</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2225465</t>
+          <t>2168112</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3173963</t>
+          <t>3166776</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3403309</t>
+          <t>3398691</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3481354</t>
+          <t>3480319</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5529591</t>
+          <t>5575882</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6621651</t>
+          <t>6621270</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>47000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74545</t>
+          <t>74821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35236</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46188</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>327693</t>
+          <t>337403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>296046</t>
+          <t>310613</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>353099</t>
+          <t>360583</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>267824</t>
+          <t>309341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247494</t>
+          <t>289111</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>283763</t>
+          <t>325837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>595516</t>
+          <t>646744</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>559812</t>
+          <t>613492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>622951</t>
+          <t>676794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,86%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>34282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>40483</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22807</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>57338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22297</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,67 +1894,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>24713</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>14551</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>40288</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>23266</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>13395</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>38029</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1972,27 +1972,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>32941</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>365996</t>
+          <t>412941</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>345342</t>
+          <t>393725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384049</t>
+          <t>431098</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>472531</t>
+          <t>459045</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>456444</t>
+          <t>443482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>487584</t>
+          <t>470318</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>838527</t>
+          <t>871986</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>809115</t>
+          <t>843341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>861366</t>
+          <t>894791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20147</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29998</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>46249</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>59296</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,22 +2498,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -2541,22 +2541,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>811</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>492610</t>
+          <t>568350</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>478511</t>
+          <t>553140</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>503982</t>
+          <t>580790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>507664</t>
+          <t>581856</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>496905</t>
+          <t>570843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>515021</t>
+          <t>590875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1000273</t>
+          <t>1150204</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>984924</t>
+          <t>1132696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1016299</t>
+          <t>1166943</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>28353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43833</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37616</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40612</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>601357</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>247420</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>758973</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>593525</t>
+          <t>643993</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>252642</t>
+          <t>627704</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>827449</t>
+          <t>656310</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>667313</t>
+          <t>692124</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>646515</t>
+          <t>680786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>677219</t>
+          <t>701141</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1260837</t>
+          <t>1336118</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>775126</t>
+          <t>1317634</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1498067</t>
+          <t>1351494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,27 +3975,27 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,22 +4166,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>855</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>855</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>526202</t>
+          <t>569747</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>515649</t>
+          <t>556403</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>535978</t>
+          <t>579409</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>523364</t>
+          <t>582205</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>516044</t>
+          <t>574215</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>529603</t>
+          <t>588725</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1049567</t>
+          <t>1151953</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1036231</t>
+          <t>1139016</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1061493</t>
+          <t>1166418</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>18471</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>590</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>590</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,67 +5187,67 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>6262</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>2237</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>6109</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>353944</t>
+          <t>390165</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>346142</t>
+          <t>381599</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>358894</t>
+          <t>396430</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>589859</t>
+          <t>419342</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>578247</t>
+          <t>412577</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>601232</t>
+          <t>424472</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>943803</t>
+          <t>809507</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>931676</t>
+          <t>798723</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>959172</t>
+          <t>817377</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,22 +5565,22 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19474</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>274023</t>
+          <t>300095</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>267990</t>
+          <t>292410</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>411341</t>
+          <t>448967</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>405541</t>
+          <t>442917</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>415782</t>
+          <t>453439</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>685363</t>
+          <t>749063</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>677329</t>
+          <t>738980</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>691885</t>
+          <t>755874</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>119264</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>147680</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>90221</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>137908</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>224253</t>
+          <t>244844</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>187718</t>
+          <t>211190</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>261841</t>
+          <t>276669</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6403,67 +6403,67 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>37660</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>27356</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>48890</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>40760</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>28501</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>63309</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,27 +6473,27 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>80404</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>118721</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>29843</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>51980</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>88272</t>
+          <t>93838</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6742,69 +6742,69 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1088058</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>19723</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>11981</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>33565</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>8357</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>28950</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>293424</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1207587</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2933993</t>
+          <t>3222696</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2168112</t>
+          <t>3173821</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3166776</t>
+          <t>3261218</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3439894</t>
+          <t>3492880</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3398691</t>
+          <t>3459627</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3480319</t>
+          <t>3520318</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>6373886</t>
+          <t>6715575</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5575882</t>
+          <t>6665986</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6621270</t>
+          <t>6768208</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
